--- a/output/upload/S00026_1809_연금저축_미래로기업복지연금보험.xlsx
+++ b/output/upload/S00026_1809_연금저축_미래로기업복지연금보험.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV22"/>
+  <dimension ref="A1:AV188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -1321,10 +1321,10 @@
       </c>
       <c r="I7" s="6" t="n"/>
       <c r="J7" s="6" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
@@ -1333,17 +1333,9 @@
       </c>
       <c r="M7" s="6" t="n"/>
       <c r="N7" s="6" t="n"/>
-      <c r="O7" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="P7" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q7" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="O7" s="6" t="n"/>
+      <c r="P7" s="6" t="n"/>
+      <c r="Q7" s="6" t="n"/>
       <c r="R7" s="6" t="n"/>
       <c r="S7" s="6" t="n"/>
       <c r="T7" s="6" t="n"/>
@@ -1351,14 +1343,14 @@
       <c r="V7" s="6" t="n"/>
       <c r="W7" s="6" t="n"/>
       <c r="X7" s="6" t="n">
-        <v>999</v>
+        <v>5</v>
       </c>
       <c r="Y7" s="6" t="n">
-        <v>999</v>
+        <v>5</v>
       </c>
       <c r="Z7" s="6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AA7" s="6" t="n"/>
@@ -1403,10 +1395,10 @@
       </c>
       <c r="I8" s="6" t="n"/>
       <c r="J8" s="6" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>110</v>
+        <v>48</v>
       </c>
       <c r="L8" s="6" t="inlineStr">
         <is>
@@ -1415,17 +1407,9 @@
       </c>
       <c r="M8" s="6" t="n"/>
       <c r="N8" s="6" t="n"/>
-      <c r="O8" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="P8" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q8" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="O8" s="6" t="n"/>
+      <c r="P8" s="6" t="n"/>
+      <c r="Q8" s="6" t="n"/>
       <c r="R8" s="6" t="n"/>
       <c r="S8" s="6" t="n"/>
       <c r="T8" s="6" t="n"/>
@@ -1433,14 +1417,14 @@
       <c r="V8" s="6" t="n"/>
       <c r="W8" s="6" t="n"/>
       <c r="X8" s="6" t="n">
-        <v>999</v>
+        <v>7</v>
       </c>
       <c r="Y8" s="6" t="n">
-        <v>999</v>
+        <v>7</v>
       </c>
       <c r="Z8" s="6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AA8" s="6" t="n"/>
@@ -1468,17 +1452,33 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="n"/>
+      <c r="B9" s="5" t="inlineStr"/>
       <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
+      <c r="D9" s="5" t="inlineStr"/>
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="6" t="n"/>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I9" s="6" t="n"/>
-      <c r="J9" s="6" t="n"/>
-      <c r="K9" s="6" t="n"/>
-      <c r="L9" s="6" t="n"/>
+      <c r="J9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M9" s="6" t="n"/>
       <c r="N9" s="6" t="n"/>
       <c r="O9" s="6" t="n"/>
@@ -1490,9 +1490,17 @@
       <c r="U9" s="6" t="n"/>
       <c r="V9" s="6" t="n"/>
       <c r="W9" s="6" t="n"/>
-      <c r="X9" s="6" t="n"/>
-      <c r="Y9" s="6" t="n"/>
-      <c r="Z9" s="6" t="n"/>
+      <c r="X9" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y9" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z9" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="AA9" s="6" t="n"/>
       <c r="AB9" s="6" t="n"/>
       <c r="AC9" s="6" t="n"/>
@@ -1518,17 +1526,33 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="n"/>
+      <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
+      <c r="D10" s="5" t="inlineStr"/>
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I10" s="6" t="n"/>
-      <c r="J10" s="6" t="n"/>
-      <c r="K10" s="6" t="n"/>
-      <c r="L10" s="6" t="n"/>
+      <c r="J10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="L10" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M10" s="6" t="n"/>
       <c r="N10" s="6" t="n"/>
       <c r="O10" s="6" t="n"/>
@@ -1540,9 +1564,17 @@
       <c r="U10" s="6" t="n"/>
       <c r="V10" s="6" t="n"/>
       <c r="W10" s="6" t="n"/>
-      <c r="X10" s="6" t="n"/>
-      <c r="Y10" s="6" t="n"/>
-      <c r="Z10" s="6" t="n"/>
+      <c r="X10" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y10" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z10" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="AA10" s="6" t="n"/>
       <c r="AB10" s="6" t="n"/>
       <c r="AC10" s="6" t="n"/>
@@ -1568,17 +1600,33 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="n"/>
+      <c r="B11" s="5" t="inlineStr"/>
       <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
+      <c r="D11" s="5" t="inlineStr"/>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="6" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I11" s="6" t="n"/>
-      <c r="J11" s="6" t="n"/>
-      <c r="K11" s="6" t="n"/>
-      <c r="L11" s="6" t="n"/>
+      <c r="J11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="L11" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M11" s="6" t="n"/>
       <c r="N11" s="6" t="n"/>
       <c r="O11" s="6" t="n"/>
@@ -1590,9 +1638,17 @@
       <c r="U11" s="6" t="n"/>
       <c r="V11" s="6" t="n"/>
       <c r="W11" s="6" t="n"/>
-      <c r="X11" s="6" t="n"/>
-      <c r="Y11" s="6" t="n"/>
-      <c r="Z11" s="6" t="n"/>
+      <c r="X11" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y11" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z11" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="AA11" s="6" t="n"/>
       <c r="AB11" s="6" t="n"/>
       <c r="AC11" s="6" t="n"/>
@@ -1618,17 +1674,33 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="n"/>
+      <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
+      <c r="D12" s="5" t="inlineStr"/>
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="6" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I12" s="6" t="n"/>
-      <c r="J12" s="6" t="n"/>
-      <c r="K12" s="6" t="n"/>
-      <c r="L12" s="6" t="n"/>
+      <c r="J12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="L12" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M12" s="6" t="n"/>
       <c r="N12" s="6" t="n"/>
       <c r="O12" s="6" t="n"/>
@@ -1640,9 +1712,17 @@
       <c r="U12" s="6" t="n"/>
       <c r="V12" s="6" t="n"/>
       <c r="W12" s="6" t="n"/>
-      <c r="X12" s="6" t="n"/>
-      <c r="Y12" s="6" t="n"/>
-      <c r="Z12" s="6" t="n"/>
+      <c r="X12" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="Y12" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z12" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AA12" s="6" t="n"/>
       <c r="AB12" s="6" t="n"/>
       <c r="AC12" s="6" t="n"/>
@@ -1668,17 +1748,33 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="n"/>
+      <c r="B13" s="5" t="inlineStr"/>
       <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
+      <c r="D13" s="5" t="inlineStr"/>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I13" s="6" t="n"/>
-      <c r="J13" s="6" t="n"/>
-      <c r="K13" s="6" t="n"/>
-      <c r="L13" s="6" t="n"/>
+      <c r="J13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M13" s="6" t="n"/>
       <c r="N13" s="6" t="n"/>
       <c r="O13" s="6" t="n"/>
@@ -1690,9 +1786,17 @@
       <c r="U13" s="6" t="n"/>
       <c r="V13" s="6" t="n"/>
       <c r="W13" s="6" t="n"/>
-      <c r="X13" s="6" t="n"/>
-      <c r="Y13" s="6" t="n"/>
-      <c r="Z13" s="6" t="n"/>
+      <c r="X13" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y13" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z13" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="AA13" s="6" t="n"/>
       <c r="AB13" s="6" t="n"/>
       <c r="AC13" s="6" t="n"/>
@@ -1718,17 +1822,33 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="n"/>
+      <c r="B14" s="5" t="inlineStr"/>
       <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
+      <c r="D14" s="5" t="inlineStr"/>
       <c r="E14" s="5" t="n"/>
       <c r="F14" s="5" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I14" s="6" t="n"/>
-      <c r="J14" s="6" t="n"/>
-      <c r="K14" s="6" t="n"/>
-      <c r="L14" s="6" t="n"/>
+      <c r="J14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M14" s="6" t="n"/>
       <c r="N14" s="6" t="n"/>
       <c r="O14" s="6" t="n"/>
@@ -1740,9 +1860,17 @@
       <c r="U14" s="6" t="n"/>
       <c r="V14" s="6" t="n"/>
       <c r="W14" s="6" t="n"/>
-      <c r="X14" s="6" t="n"/>
-      <c r="Y14" s="6" t="n"/>
-      <c r="Z14" s="6" t="n"/>
+      <c r="X14" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y14" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z14" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="AA14" s="6" t="n"/>
       <c r="AB14" s="6" t="n"/>
       <c r="AC14" s="6" t="n"/>
@@ -1768,17 +1896,33 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="n"/>
+      <c r="B15" s="5" t="inlineStr"/>
       <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
+      <c r="D15" s="5" t="inlineStr"/>
       <c r="E15" s="5" t="n"/>
       <c r="F15" s="5" t="n"/>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I15" s="6" t="n"/>
-      <c r="J15" s="6" t="n"/>
-      <c r="K15" s="6" t="n"/>
-      <c r="L15" s="6" t="n"/>
+      <c r="J15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M15" s="6" t="n"/>
       <c r="N15" s="6" t="n"/>
       <c r="O15" s="6" t="n"/>
@@ -1790,9 +1934,17 @@
       <c r="U15" s="6" t="n"/>
       <c r="V15" s="6" t="n"/>
       <c r="W15" s="6" t="n"/>
-      <c r="X15" s="6" t="n"/>
-      <c r="Y15" s="6" t="n"/>
-      <c r="Z15" s="6" t="n"/>
+      <c r="X15" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y15" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z15" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="AA15" s="6" t="n"/>
       <c r="AB15" s="6" t="n"/>
       <c r="AC15" s="6" t="n"/>
@@ -1818,17 +1970,33 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
-      <c r="B16" s="5" t="n"/>
+      <c r="B16" s="5" t="inlineStr"/>
       <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="n"/>
+      <c r="D16" s="5" t="inlineStr"/>
       <c r="E16" s="5" t="n"/>
       <c r="F16" s="5" t="n"/>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="6" t="n"/>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I16" s="6" t="n"/>
-      <c r="J16" s="6" t="n"/>
-      <c r="K16" s="6" t="n"/>
-      <c r="L16" s="6" t="n"/>
+      <c r="J16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M16" s="6" t="n"/>
       <c r="N16" s="6" t="n"/>
       <c r="O16" s="6" t="n"/>
@@ -1840,9 +2008,17 @@
       <c r="U16" s="6" t="n"/>
       <c r="V16" s="6" t="n"/>
       <c r="W16" s="6" t="n"/>
-      <c r="X16" s="6" t="n"/>
-      <c r="Y16" s="6" t="n"/>
-      <c r="Z16" s="6" t="n"/>
+      <c r="X16" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y16" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z16" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="AA16" s="6" t="n"/>
       <c r="AB16" s="6" t="n"/>
       <c r="AC16" s="6" t="n"/>
@@ -1868,17 +2044,33 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="n"/>
+      <c r="B17" s="5" t="inlineStr"/>
       <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
+      <c r="D17" s="5" t="inlineStr"/>
       <c r="E17" s="5" t="n"/>
       <c r="F17" s="5" t="n"/>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="6" t="n"/>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I17" s="6" t="n"/>
-      <c r="J17" s="6" t="n"/>
-      <c r="K17" s="6" t="n"/>
-      <c r="L17" s="6" t="n"/>
+      <c r="J17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M17" s="6" t="n"/>
       <c r="N17" s="6" t="n"/>
       <c r="O17" s="6" t="n"/>
@@ -1890,9 +2082,17 @@
       <c r="U17" s="6" t="n"/>
       <c r="V17" s="6" t="n"/>
       <c r="W17" s="6" t="n"/>
-      <c r="X17" s="6" t="n"/>
-      <c r="Y17" s="6" t="n"/>
-      <c r="Z17" s="6" t="n"/>
+      <c r="X17" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y17" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z17" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="AA17" s="6" t="n"/>
       <c r="AB17" s="6" t="n"/>
       <c r="AC17" s="6" t="n"/>
@@ -1918,17 +2118,33 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
-      <c r="B18" s="5" t="n"/>
+      <c r="B18" s="5" t="inlineStr"/>
       <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
+      <c r="D18" s="5" t="inlineStr"/>
       <c r="E18" s="5" t="n"/>
       <c r="F18" s="5" t="n"/>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="6" t="n"/>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I18" s="6" t="n"/>
-      <c r="J18" s="6" t="n"/>
-      <c r="K18" s="6" t="n"/>
-      <c r="L18" s="6" t="n"/>
+      <c r="J18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M18" s="6" t="n"/>
       <c r="N18" s="6" t="n"/>
       <c r="O18" s="6" t="n"/>
@@ -1940,9 +2156,17 @@
       <c r="U18" s="6" t="n"/>
       <c r="V18" s="6" t="n"/>
       <c r="W18" s="6" t="n"/>
-      <c r="X18" s="6" t="n"/>
-      <c r="Y18" s="6" t="n"/>
-      <c r="Z18" s="6" t="n"/>
+      <c r="X18" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="Y18" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="Z18" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AA18" s="6" t="n"/>
       <c r="AB18" s="6" t="n"/>
       <c r="AC18" s="6" t="n"/>
@@ -1968,17 +2192,33 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
-      <c r="B19" s="5" t="n"/>
+      <c r="B19" s="5" t="inlineStr"/>
       <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
+      <c r="D19" s="5" t="inlineStr"/>
       <c r="E19" s="5" t="n"/>
       <c r="F19" s="5" t="n"/>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="6" t="n"/>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I19" s="6" t="n"/>
-      <c r="J19" s="6" t="n"/>
-      <c r="K19" s="6" t="n"/>
-      <c r="L19" s="6" t="n"/>
+      <c r="J19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="L19" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M19" s="6" t="n"/>
       <c r="N19" s="6" t="n"/>
       <c r="O19" s="6" t="n"/>
@@ -1990,9 +2230,17 @@
       <c r="U19" s="6" t="n"/>
       <c r="V19" s="6" t="n"/>
       <c r="W19" s="6" t="n"/>
-      <c r="X19" s="6" t="n"/>
-      <c r="Y19" s="6" t="n"/>
-      <c r="Z19" s="6" t="n"/>
+      <c r="X19" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y19" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z19" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="AA19" s="6" t="n"/>
       <c r="AB19" s="6" t="n"/>
       <c r="AC19" s="6" t="n"/>
@@ -2018,17 +2266,33 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
-      <c r="B20" s="5" t="n"/>
+      <c r="B20" s="5" t="inlineStr"/>
       <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
+      <c r="D20" s="5" t="inlineStr"/>
       <c r="E20" s="5" t="n"/>
       <c r="F20" s="5" t="n"/>
-      <c r="G20" s="6" t="n"/>
-      <c r="H20" s="6" t="n"/>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I20" s="6" t="n"/>
-      <c r="J20" s="6" t="n"/>
-      <c r="K20" s="6" t="n"/>
-      <c r="L20" s="6" t="n"/>
+      <c r="J20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="L20" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M20" s="6" t="n"/>
       <c r="N20" s="6" t="n"/>
       <c r="O20" s="6" t="n"/>
@@ -2040,9 +2304,17 @@
       <c r="U20" s="6" t="n"/>
       <c r="V20" s="6" t="n"/>
       <c r="W20" s="6" t="n"/>
-      <c r="X20" s="6" t="n"/>
-      <c r="Y20" s="6" t="n"/>
-      <c r="Z20" s="6" t="n"/>
+      <c r="X20" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y20" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z20" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="AA20" s="6" t="n"/>
       <c r="AB20" s="6" t="n"/>
       <c r="AC20" s="6" t="n"/>
@@ -2068,17 +2340,33 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
-      <c r="B21" s="5" t="n"/>
+      <c r="B21" s="5" t="inlineStr"/>
       <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
+      <c r="D21" s="5" t="inlineStr"/>
       <c r="E21" s="5" t="n"/>
       <c r="F21" s="5" t="n"/>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="6" t="n"/>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I21" s="6" t="n"/>
-      <c r="J21" s="6" t="n"/>
-      <c r="K21" s="6" t="n"/>
-      <c r="L21" s="6" t="n"/>
+      <c r="J21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="L21" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M21" s="6" t="n"/>
       <c r="N21" s="6" t="n"/>
       <c r="O21" s="6" t="n"/>
@@ -2090,9 +2378,17 @@
       <c r="U21" s="6" t="n"/>
       <c r="V21" s="6" t="n"/>
       <c r="W21" s="6" t="n"/>
-      <c r="X21" s="6" t="n"/>
-      <c r="Y21" s="6" t="n"/>
-      <c r="Z21" s="6" t="n"/>
+      <c r="X21" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y21" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z21" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="AA21" s="6" t="n"/>
       <c r="AB21" s="6" t="n"/>
       <c r="AC21" s="6" t="n"/>
@@ -2118,17 +2414,33 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
-      <c r="B22" s="5" t="n"/>
+      <c r="B22" s="5" t="inlineStr"/>
       <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
+      <c r="D22" s="5" t="inlineStr"/>
       <c r="E22" s="5" t="n"/>
       <c r="F22" s="5" t="n"/>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="6" t="n"/>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I22" s="6" t="n"/>
-      <c r="J22" s="6" t="n"/>
-      <c r="K22" s="6" t="n"/>
-      <c r="L22" s="6" t="n"/>
+      <c r="J22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="L22" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M22" s="6" t="n"/>
       <c r="N22" s="6" t="n"/>
       <c r="O22" s="6" t="n"/>
@@ -2140,9 +2452,17 @@
       <c r="U22" s="6" t="n"/>
       <c r="V22" s="6" t="n"/>
       <c r="W22" s="6" t="n"/>
-      <c r="X22" s="6" t="n"/>
-      <c r="Y22" s="6" t="n"/>
-      <c r="Z22" s="6" t="n"/>
+      <c r="X22" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y22" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z22" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="AA22" s="6" t="n"/>
       <c r="AB22" s="6" t="n"/>
       <c r="AC22" s="6" t="n"/>
@@ -2166,6 +2486,5982 @@
       <c r="AU22" s="6" t="n"/>
       <c r="AV22" s="6" t="n"/>
     </row>
+    <row r="23">
+      <c r="B23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>37</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X23" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>47</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X24" t="n">
+        <v>57</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>57</v>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>53</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X25" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>51</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X26" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>48</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X27" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>43</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X28" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>38</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X29" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>48</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X30" t="n">
+        <v>58</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>58</v>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>54</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X31" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>52</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X32" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>49</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X33" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>44</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X34" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>39</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X35" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>49</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X36" t="n">
+        <v>59</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>59</v>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>55</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X37" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>53</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X38" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>50</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X39" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>45</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X40" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>40</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X41" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>50</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X42" t="n">
+        <v>60</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>56</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X43" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>54</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X44" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>51</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X45" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>46</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X46" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>41</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X47" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>51</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X48" t="n">
+        <v>61</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>61</v>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>57</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X49" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>55</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X50" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>52</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X51" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>47</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X52" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>42</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X53" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>52</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X54" t="n">
+        <v>62</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>62</v>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>58</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X55" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>56</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X56" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>53</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X57" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>48</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X58" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>43</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X59" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>53</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X60" t="n">
+        <v>63</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>63</v>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
+        <v>59</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X61" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>57</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X62" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
+        <v>54</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X63" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
+        <v>49</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X64" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>44</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X65" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
+        <v>54</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X66" t="n">
+        <v>64</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>60</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X67" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
+        <v>58</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X68" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="inlineStr"/>
+      <c r="D69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>55</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X69" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="inlineStr"/>
+      <c r="D70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>50</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X70" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>45</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X71" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
+        <v>55</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X72" t="n">
+        <v>65</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>65</v>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
+        <v>61</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X73" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="inlineStr"/>
+      <c r="D74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="n">
+        <v>59</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X74" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="inlineStr"/>
+      <c r="D75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>56</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X75" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="inlineStr"/>
+      <c r="D76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
+        <v>51</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X76" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="inlineStr"/>
+      <c r="D77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>46</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X77" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="inlineStr"/>
+      <c r="D78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
+        <v>56</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X78" t="n">
+        <v>66</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>66</v>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="inlineStr"/>
+      <c r="D79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="n">
+        <v>62</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X79" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="inlineStr"/>
+      <c r="D80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
+        <v>60</v>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X80" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="inlineStr"/>
+      <c r="D81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="n">
+        <v>57</v>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X81" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="inlineStr"/>
+      <c r="D82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" t="n">
+        <v>52</v>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X82" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="inlineStr"/>
+      <c r="D83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="n">
+        <v>47</v>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X83" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="inlineStr"/>
+      <c r="D84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" t="n">
+        <v>57</v>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X84" t="n">
+        <v>67</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>67</v>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="inlineStr"/>
+      <c r="D85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" t="n">
+        <v>63</v>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X85" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="inlineStr"/>
+      <c r="D86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" t="n">
+        <v>61</v>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X86" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y86" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="inlineStr"/>
+      <c r="D87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" t="n">
+        <v>58</v>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X87" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y87" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="inlineStr"/>
+      <c r="D88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" t="n">
+        <v>53</v>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X88" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="inlineStr"/>
+      <c r="D89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" t="n">
+        <v>48</v>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X89" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="inlineStr"/>
+      <c r="D90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="n">
+        <v>58</v>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X90" t="n">
+        <v>68</v>
+      </c>
+      <c r="Y90" t="n">
+        <v>68</v>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="inlineStr"/>
+      <c r="D91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
+        <v>64</v>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X91" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y91" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="inlineStr"/>
+      <c r="D92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" t="n">
+        <v>62</v>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X92" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y92" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="inlineStr"/>
+      <c r="D93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" t="n">
+        <v>59</v>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X93" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="inlineStr"/>
+      <c r="D94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" t="n">
+        <v>54</v>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X94" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y94" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="inlineStr"/>
+      <c r="D95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" t="n">
+        <v>49</v>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X95" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y95" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="inlineStr"/>
+      <c r="D96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" t="n">
+        <v>59</v>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X96" t="n">
+        <v>69</v>
+      </c>
+      <c r="Y96" t="n">
+        <v>69</v>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="inlineStr"/>
+      <c r="D97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="n">
+        <v>65</v>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X97" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y97" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" t="inlineStr"/>
+      <c r="D98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" t="n">
+        <v>63</v>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X98" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y98" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" t="inlineStr"/>
+      <c r="D99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" t="n">
+        <v>60</v>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X99" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y99" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" t="inlineStr"/>
+      <c r="D100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="n">
+        <v>55</v>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X100" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y100" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" t="inlineStr"/>
+      <c r="D101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" t="n">
+        <v>50</v>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X101" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y101" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" t="inlineStr"/>
+      <c r="D102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
+        <v>60</v>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X102" t="n">
+        <v>70</v>
+      </c>
+      <c r="Y102" t="n">
+        <v>70</v>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" t="inlineStr"/>
+      <c r="D103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" t="n">
+        <v>66</v>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X103" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y103" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" t="inlineStr"/>
+      <c r="D104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" t="n">
+        <v>64</v>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X104" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y104" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" t="inlineStr"/>
+      <c r="D105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" t="n">
+        <v>61</v>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X105" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y105" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" t="inlineStr"/>
+      <c r="D106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" t="n">
+        <v>56</v>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X106" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y106" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" t="inlineStr"/>
+      <c r="D107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="n">
+        <v>51</v>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X107" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y107" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" t="inlineStr"/>
+      <c r="D108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" t="n">
+        <v>61</v>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X108" t="n">
+        <v>71</v>
+      </c>
+      <c r="Y108" t="n">
+        <v>71</v>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" t="inlineStr"/>
+      <c r="D109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J109" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" t="n">
+        <v>67</v>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X109" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y109" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" t="inlineStr"/>
+      <c r="D110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J110" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" t="n">
+        <v>65</v>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X110" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y110" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" t="inlineStr"/>
+      <c r="D111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J111" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" t="n">
+        <v>62</v>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X111" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" t="inlineStr"/>
+      <c r="D112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J112" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" t="n">
+        <v>57</v>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X112" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y112" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" t="inlineStr"/>
+      <c r="D113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" t="n">
+        <v>52</v>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X113" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y113" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" t="inlineStr"/>
+      <c r="D114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J114" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" t="n">
+        <v>62</v>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X114" t="n">
+        <v>72</v>
+      </c>
+      <c r="Y114" t="n">
+        <v>72</v>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" t="inlineStr"/>
+      <c r="D115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J115" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" t="n">
+        <v>68</v>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X115" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y115" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" t="inlineStr"/>
+      <c r="D116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" t="n">
+        <v>66</v>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X116" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y116" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" t="inlineStr"/>
+      <c r="D117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J117" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" t="n">
+        <v>63</v>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X117" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" t="inlineStr"/>
+      <c r="D118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J118" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" t="n">
+        <v>58</v>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X118" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" t="inlineStr"/>
+      <c r="D119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" t="n">
+        <v>53</v>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X119" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" t="inlineStr"/>
+      <c r="D120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" t="n">
+        <v>63</v>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X120" t="n">
+        <v>73</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>73</v>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" t="inlineStr"/>
+      <c r="D121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J121" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" t="n">
+        <v>69</v>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X121" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" t="inlineStr"/>
+      <c r="D122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J122" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" t="n">
+        <v>67</v>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X122" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" t="inlineStr"/>
+      <c r="D123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" t="n">
+        <v>64</v>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X123" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" t="inlineStr"/>
+      <c r="D124" t="inlineStr"/>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J124" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" t="n">
+        <v>59</v>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X124" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" t="inlineStr"/>
+      <c r="D125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" t="n">
+        <v>54</v>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X125" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" t="inlineStr"/>
+      <c r="D126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" t="n">
+        <v>64</v>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X126" t="n">
+        <v>74</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>74</v>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" t="inlineStr"/>
+      <c r="D127" t="inlineStr"/>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" t="n">
+        <v>70</v>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X127" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" t="inlineStr"/>
+      <c r="D128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" t="n">
+        <v>68</v>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X128" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" t="inlineStr"/>
+      <c r="D129" t="inlineStr"/>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" t="n">
+        <v>65</v>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X129" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" t="inlineStr"/>
+      <c r="D130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J130" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" t="n">
+        <v>60</v>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X130" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" t="inlineStr"/>
+      <c r="D131" t="inlineStr"/>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J131" t="n">
+        <v>0</v>
+      </c>
+      <c r="K131" t="n">
+        <v>55</v>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X131" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" t="inlineStr"/>
+      <c r="D132" t="inlineStr"/>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J132" t="n">
+        <v>0</v>
+      </c>
+      <c r="K132" t="n">
+        <v>65</v>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X132" t="n">
+        <v>75</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>75</v>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" t="inlineStr"/>
+      <c r="D133" t="inlineStr"/>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" t="n">
+        <v>71</v>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X133" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" t="inlineStr"/>
+      <c r="D134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J134" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" t="n">
+        <v>69</v>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X134" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" t="inlineStr"/>
+      <c r="D135" t="inlineStr"/>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J135" t="n">
+        <v>0</v>
+      </c>
+      <c r="K135" t="n">
+        <v>66</v>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X135" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" t="inlineStr"/>
+      <c r="D136" t="inlineStr"/>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" t="n">
+        <v>61</v>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X136" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="B137" t="inlineStr"/>
+      <c r="D137" t="inlineStr"/>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J137" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" t="n">
+        <v>56</v>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X137" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" t="inlineStr"/>
+      <c r="D138" t="inlineStr"/>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J138" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" t="n">
+        <v>66</v>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X138" t="n">
+        <v>76</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>76</v>
+      </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" t="inlineStr"/>
+      <c r="D139" t="inlineStr"/>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J139" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" t="n">
+        <v>72</v>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X139" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140" t="inlineStr"/>
+      <c r="D140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" t="n">
+        <v>70</v>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X140" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="B141" t="inlineStr"/>
+      <c r="D141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K141" t="n">
+        <v>67</v>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X141" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" t="inlineStr"/>
+      <c r="D142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J142" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" t="n">
+        <v>62</v>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X142" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" t="inlineStr"/>
+      <c r="D143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J143" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" t="n">
+        <v>57</v>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X143" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="B144" t="inlineStr"/>
+      <c r="D144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J144" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" t="n">
+        <v>67</v>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X144" t="n">
+        <v>77</v>
+      </c>
+      <c r="Y144" t="n">
+        <v>77</v>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" t="inlineStr"/>
+      <c r="D145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J145" t="n">
+        <v>0</v>
+      </c>
+      <c r="K145" t="n">
+        <v>73</v>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X145" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y145" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" t="inlineStr"/>
+      <c r="D146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J146" t="n">
+        <v>0</v>
+      </c>
+      <c r="K146" t="n">
+        <v>71</v>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X146" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y146" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="B147" t="inlineStr"/>
+      <c r="D147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J147" t="n">
+        <v>0</v>
+      </c>
+      <c r="K147" t="n">
+        <v>68</v>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X147" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="B148" t="inlineStr"/>
+      <c r="D148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J148" t="n">
+        <v>0</v>
+      </c>
+      <c r="K148" t="n">
+        <v>63</v>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X148" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y148" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="B149" t="inlineStr"/>
+      <c r="D149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J149" t="n">
+        <v>0</v>
+      </c>
+      <c r="K149" t="n">
+        <v>58</v>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X149" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y149" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="B150" t="inlineStr"/>
+      <c r="D150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J150" t="n">
+        <v>0</v>
+      </c>
+      <c r="K150" t="n">
+        <v>68</v>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X150" t="n">
+        <v>78</v>
+      </c>
+      <c r="Y150" t="n">
+        <v>78</v>
+      </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" t="inlineStr"/>
+      <c r="D151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J151" t="n">
+        <v>0</v>
+      </c>
+      <c r="K151" t="n">
+        <v>74</v>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X151" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y151" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="B152" t="inlineStr"/>
+      <c r="D152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J152" t="n">
+        <v>0</v>
+      </c>
+      <c r="K152" t="n">
+        <v>72</v>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X152" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y152" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" t="inlineStr"/>
+      <c r="D153" t="inlineStr"/>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J153" t="n">
+        <v>0</v>
+      </c>
+      <c r="K153" t="n">
+        <v>69</v>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X153" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y153" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" t="inlineStr"/>
+      <c r="D154" t="inlineStr"/>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J154" t="n">
+        <v>0</v>
+      </c>
+      <c r="K154" t="n">
+        <v>64</v>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X154" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y154" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="B155" t="inlineStr"/>
+      <c r="D155" t="inlineStr"/>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J155" t="n">
+        <v>0</v>
+      </c>
+      <c r="K155" t="n">
+        <v>59</v>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X155" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y155" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" t="inlineStr"/>
+      <c r="D156" t="inlineStr"/>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J156" t="n">
+        <v>0</v>
+      </c>
+      <c r="K156" t="n">
+        <v>69</v>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X156" t="n">
+        <v>79</v>
+      </c>
+      <c r="Y156" t="n">
+        <v>79</v>
+      </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="B157" t="inlineStr"/>
+      <c r="D157" t="inlineStr"/>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J157" t="n">
+        <v>0</v>
+      </c>
+      <c r="K157" t="n">
+        <v>75</v>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X157" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y157" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" t="inlineStr"/>
+      <c r="D158" t="inlineStr"/>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J158" t="n">
+        <v>0</v>
+      </c>
+      <c r="K158" t="n">
+        <v>73</v>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X158" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y158" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="B159" t="inlineStr"/>
+      <c r="D159" t="inlineStr"/>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J159" t="n">
+        <v>0</v>
+      </c>
+      <c r="K159" t="n">
+        <v>70</v>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X159" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y159" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="B160" t="inlineStr"/>
+      <c r="D160" t="inlineStr"/>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J160" t="n">
+        <v>0</v>
+      </c>
+      <c r="K160" t="n">
+        <v>65</v>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X160" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y160" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" t="inlineStr"/>
+      <c r="D161" t="inlineStr"/>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J161" t="n">
+        <v>0</v>
+      </c>
+      <c r="K161" t="n">
+        <v>60</v>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X161" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y161" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" t="inlineStr"/>
+      <c r="D162" t="inlineStr"/>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J162" t="n">
+        <v>0</v>
+      </c>
+      <c r="K162" t="n">
+        <v>70</v>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X162" t="n">
+        <v>80</v>
+      </c>
+      <c r="Y162" t="n">
+        <v>80</v>
+      </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" t="inlineStr"/>
+      <c r="D163" t="inlineStr"/>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J163" t="n">
+        <v>0</v>
+      </c>
+      <c r="K163" t="n">
+        <v>54</v>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X163" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y163" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="B164" t="inlineStr"/>
+      <c r="D164" t="inlineStr"/>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J164" t="n">
+        <v>0</v>
+      </c>
+      <c r="K164" t="n">
+        <v>55</v>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X164" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y164" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="B165" t="inlineStr"/>
+      <c r="D165" t="inlineStr"/>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J165" t="n">
+        <v>0</v>
+      </c>
+      <c r="K165" t="n">
+        <v>56</v>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X165" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y165" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="B166" t="inlineStr"/>
+      <c r="D166" t="inlineStr"/>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J166" t="n">
+        <v>0</v>
+      </c>
+      <c r="K166" t="n">
+        <v>57</v>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X166" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y166" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="B167" t="inlineStr"/>
+      <c r="D167" t="inlineStr"/>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J167" t="n">
+        <v>0</v>
+      </c>
+      <c r="K167" t="n">
+        <v>58</v>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="B168" t="inlineStr"/>
+      <c r="D168" t="inlineStr"/>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J168" t="n">
+        <v>0</v>
+      </c>
+      <c r="K168" t="n">
+        <v>59</v>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X168" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y168" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="B169" t="inlineStr"/>
+      <c r="D169" t="inlineStr"/>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J169" t="n">
+        <v>0</v>
+      </c>
+      <c r="K169" t="n">
+        <v>60</v>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X169" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y169" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="B170" t="inlineStr"/>
+      <c r="D170" t="inlineStr"/>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K170" t="n">
+        <v>61</v>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X170" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y170" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" t="inlineStr"/>
+      <c r="D171" t="inlineStr"/>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J171" t="n">
+        <v>0</v>
+      </c>
+      <c r="K171" t="n">
+        <v>62</v>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X171" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y171" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" t="inlineStr"/>
+      <c r="D172" t="inlineStr"/>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J172" t="n">
+        <v>0</v>
+      </c>
+      <c r="K172" t="n">
+        <v>63</v>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X172" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y172" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" t="inlineStr"/>
+      <c r="D173" t="inlineStr"/>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J173" t="n">
+        <v>0</v>
+      </c>
+      <c r="K173" t="n">
+        <v>64</v>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X173" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y173" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" t="inlineStr"/>
+      <c r="D174" t="inlineStr"/>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J174" t="n">
+        <v>0</v>
+      </c>
+      <c r="K174" t="n">
+        <v>65</v>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X174" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y174" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z174" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="B175" t="inlineStr"/>
+      <c r="D175" t="inlineStr"/>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J175" t="n">
+        <v>0</v>
+      </c>
+      <c r="K175" t="n">
+        <v>66</v>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X175" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y175" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="B176" t="inlineStr"/>
+      <c r="D176" t="inlineStr"/>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J176" t="n">
+        <v>0</v>
+      </c>
+      <c r="K176" t="n">
+        <v>67</v>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X176" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y176" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="B177" t="inlineStr"/>
+      <c r="D177" t="inlineStr"/>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J177" t="n">
+        <v>0</v>
+      </c>
+      <c r="K177" t="n">
+        <v>68</v>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X177" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y177" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="B178" t="inlineStr"/>
+      <c r="D178" t="inlineStr"/>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J178" t="n">
+        <v>0</v>
+      </c>
+      <c r="K178" t="n">
+        <v>69</v>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X178" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y178" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="B179" t="inlineStr"/>
+      <c r="D179" t="inlineStr"/>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J179" t="n">
+        <v>0</v>
+      </c>
+      <c r="K179" t="n">
+        <v>70</v>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X179" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y179" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="B180" t="inlineStr"/>
+      <c r="D180" t="inlineStr"/>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K180" t="n">
+        <v>71</v>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X180" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y180" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="B181" t="inlineStr"/>
+      <c r="D181" t="inlineStr"/>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J181" t="n">
+        <v>0</v>
+      </c>
+      <c r="K181" t="n">
+        <v>72</v>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X181" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y181" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z181" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="B182" t="inlineStr"/>
+      <c r="D182" t="inlineStr"/>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J182" t="n">
+        <v>0</v>
+      </c>
+      <c r="K182" t="n">
+        <v>73</v>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X182" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y182" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z182" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="B183" t="inlineStr"/>
+      <c r="D183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J183" t="n">
+        <v>0</v>
+      </c>
+      <c r="K183" t="n">
+        <v>74</v>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X183" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y183" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z183" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="B184" t="inlineStr"/>
+      <c r="D184" t="inlineStr"/>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J184" t="n">
+        <v>0</v>
+      </c>
+      <c r="K184" t="n">
+        <v>75</v>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X184" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y184" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z184" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="B185" t="inlineStr"/>
+      <c r="D185" t="inlineStr"/>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J185" t="n">
+        <v>0</v>
+      </c>
+      <c r="K185" t="n">
+        <v>76</v>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X185" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y185" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="B186" t="inlineStr"/>
+      <c r="D186" t="inlineStr"/>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J186" t="n">
+        <v>0</v>
+      </c>
+      <c r="K186" t="n">
+        <v>77</v>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X186" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y186" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="B187" t="inlineStr"/>
+      <c r="D187" t="inlineStr"/>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J187" t="n">
+        <v>0</v>
+      </c>
+      <c r="K187" t="n">
+        <v>78</v>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X187" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y187" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="B188" t="inlineStr"/>
+      <c r="D188" t="inlineStr"/>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J188" t="n">
+        <v>0</v>
+      </c>
+      <c r="K188" t="n">
+        <v>79</v>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X188" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y188" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z188" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="L3:AV3"/>
